--- a/public/exports/29189668.xlsx
+++ b/public/exports/29189668.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215030</t>
+          <t xml:space="preserve">311215043</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -16039,7 +16039,7 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311393677</t>
+          <t xml:space="preserve">311393687</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -18139,7 +18139,7 @@
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t xml:space="preserve">311407500</t>
+          <t xml:space="preserve">311407501</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -20389,7 +20389,7 @@
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424644</t>
+          <t xml:space="preserve">311424656</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -20464,7 +20464,7 @@
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424644</t>
+          <t xml:space="preserve">311424656</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">

--- a/public/exports/29189668.xlsx
+++ b/public/exports/29189668.xlsx
@@ -5314,7 +5314,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215051</t>
+          <t xml:space="preserve">311215030</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -17614,7 +17614,7 @@
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311407501</t>
+          <t xml:space="preserve">311407500</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -19864,7 +19864,7 @@
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424656</t>
+          <t xml:space="preserve">311424644</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -19939,7 +19939,7 @@
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424656</t>
+          <t xml:space="preserve">311424644</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -24289,7 +24289,7 @@
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t xml:space="preserve">311929274</t>
+          <t xml:space="preserve">311929271</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
@@ -24364,7 +24364,7 @@
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t xml:space="preserve">311929274</t>
+          <t xml:space="preserve">311929271</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
@@ -24439,7 +24439,7 @@
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t xml:space="preserve">311929274</t>
+          <t xml:space="preserve">311929271</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t xml:space="preserve">311929274</t>
+          <t xml:space="preserve">311929271</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
